--- a/data/output/forecast_results_ml.xlsx
+++ b/data/output/forecast_results_ml.xlsx
@@ -477,20 +477,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5518.456779981118</v>
+        <v>4803.66502864943</v>
       </c>
       <c r="D2" t="n">
-        <v>4444.119559151785</v>
+        <v>3797.202706473214</v>
       </c>
       <c r="E2" t="n">
-        <v>24.44845299418315</v>
+        <v>21.54467286430364</v>
       </c>
       <c r="F2" t="n">
-        <v>25.77975951719937</v>
+        <v>21.27967990475979</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[16934.22265625, 17579.30078125, 13379.6357421875, 25094.7578125, 28190.38671875, 18284.646484375, 9756.703125]</t>
+          <t>[17732.3828125, 17583.427734375, 11592.337890625, 24708.08984375, 27090.490234375, 19709.576171875, 11969.0224609375]</t>
         </is>
       </c>
     </row>
@@ -502,24 +502,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>372.576771631274</v>
+        <v>305.8659533061498</v>
       </c>
       <c r="D3" t="n">
-        <v>345.774422781808</v>
+        <v>262.425271876819</v>
       </c>
       <c r="E3" t="n">
-        <v>24.99050456821002</v>
+        <v>20.45068952571685</v>
       </c>
       <c r="F3" t="n">
-        <v>29.32043737213067</v>
+        <v>23.6289613744599</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[1090.48974609375, 713.1672973632812, 752.8252563476562, 1095.61083984375, 1266.997314453125, 613.9191284179688, 1254.40771484375]</t>
+          <t>[1211.135055268382, 655.1662279666476, 1005.0083996957095, 1129.117521839305, 1613.3804391150566, 503.00337608035596, 1226.2120768968102]</t>
         </is>
       </c>
     </row>
@@ -535,20 +535,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>239.2409500270157</v>
+        <v>206.1163752531812</v>
       </c>
       <c r="D4" t="n">
-        <v>208.1187975818281</v>
+        <v>183.8481060097785</v>
       </c>
       <c r="E4" t="n">
-        <v>21.25540692029651</v>
+        <v>24.57090007886251</v>
       </c>
       <c r="F4" t="n">
-        <v>19.8281473648809</v>
+        <v>21.57317304403981</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[896.9918754621007, 1501.894673865982, 371.8846662461917, 1174.655573237477, 1664.5421413796103, 851.0703508658911, 1040.4183502524922]</t>
+          <t>[796.8438938325904, 1591.0021725216159, 564.0126403272873, 1151.1265679718229, 1537.4986178484758, 884.4320117620803, 1095.9748171521915]</t>
         </is>
       </c>
     </row>
@@ -564,20 +564,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>127.4017648572844</v>
+        <v>147.7305591096937</v>
       </c>
       <c r="D5" t="n">
-        <v>96.26077101375179</v>
+        <v>109.1829778806827</v>
       </c>
       <c r="E5" t="n">
-        <v>23.24031354085757</v>
+        <v>26.86850389828211</v>
       </c>
       <c r="F5" t="n">
-        <v>25.20811475503032</v>
+        <v>31.77590705353269</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[94.41043285575182, 383.62179069838703, 0.0, 690.7198984061274, 387.0108689006718, 1157.7228001670715, 664.1286086879827]</t>
+          <t>[59.121967721668966, 379.0123431139315, 0.0, 674.80072030954, 342.340661287313, 1137.3093588803754, 662.7355441414722]</t>
         </is>
       </c>
     </row>
@@ -593,20 +593,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>147.2032947847453</v>
+        <v>237.5769257290808</v>
       </c>
       <c r="D6" t="n">
-        <v>109.9412018140595</v>
+        <v>190.350125005403</v>
       </c>
       <c r="E6" t="n">
-        <v>20.21276242441443</v>
+        <v>43.58456730897895</v>
       </c>
       <c r="F6" t="n">
-        <v>22.35311142757246</v>
+        <v>38.43882723581924</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[80.0, 474.0, 355.55555555556066, 474.0, 619.0521428571441, 533.73, 987.355]</t>
+          <t>[299.7948709295644, 455.6408322037643, 335.977911898503, 422.56818141431523, 509.819258978204, 543.9260827568078, 559.2197179507702]</t>
         </is>
       </c>
     </row>
@@ -622,20 +622,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>664.8371634829214</v>
+        <v>654.6997274702309</v>
       </c>
       <c r="D7" t="n">
-        <v>581.5950753348214</v>
+        <v>541.303242274693</v>
       </c>
       <c r="E7" t="n">
-        <v>46.65011422944169</v>
+        <v>40.67742475761428</v>
       </c>
       <c r="F7" t="n">
-        <v>43.0598069976187</v>
+        <v>43.31268813080435</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[1193.834716796875, 365.8499755859375, 2097.79736328125, 2253.918212890625, 5875.28173828125, 858.6695556640625, 2455.746826171875]</t>
+          <t>[1265.97509765625, 214.92283630371094, 1984.0013427734375, 2153.0087890625, 5744.81005859375, 754.112548828125, 2171.710693359375]</t>
         </is>
       </c>
     </row>
@@ -651,20 +651,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>359.8791981569768</v>
+        <v>179.6465721905579</v>
       </c>
       <c r="D8" t="n">
-        <v>208.7248360770089</v>
+        <v>141.8370971679688</v>
       </c>
       <c r="E8" t="n">
-        <v>20.42427762120473</v>
+        <v>13.21192187812625</v>
       </c>
       <c r="F8" t="n">
-        <v>16.83192889864591</v>
+        <v>13.15496853400107</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[617.3995971679688, 545.1776123046875, 1023.94287109375, 2013.4217529296875, 937.0023193359375, 2111.26953125, 1010.0588989257812]</t>
+          <t>[513.6831665039062, 533.8416748046875, 938.7456665039062, 1733.732666015625, 786.0927124023438, 1522.7716064453125, 781.307373046875]</t>
         </is>
       </c>
     </row>
@@ -676,24 +676,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>566.3429625778709</v>
+        <v>875.3989220374739</v>
       </c>
       <c r="D9" t="n">
-        <v>492.2882087646561</v>
+        <v>679.921142578125</v>
       </c>
       <c r="E9" t="n">
-        <v>12.7872980825695</v>
+        <v>20.33447882998482</v>
       </c>
       <c r="F9" t="n">
-        <v>12.58262835080185</v>
+        <v>17.44332139815782</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[4605.0266963608465, 3947.53663322945, 4978.90920405858, 4216.009444391476, 2927.036007759923, 3087.071440744732, 4343.481479656061]</t>
+          <t>[4616.68994140625, 4640.21435546875, 4706.40771484375, 4741.896484375, 3885.731689453125, 4239.53173828125, 4325.58447265625]</t>
         </is>
       </c>
     </row>
@@ -709,20 +709,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2192.460243583337</v>
+        <v>2399.378951909501</v>
       </c>
       <c r="D10" t="n">
-        <v>2061.014182650457</v>
+        <v>2272.325304201807</v>
       </c>
       <c r="E10" t="n">
-        <v>21.02609462652315</v>
+        <v>23.42107640822731</v>
       </c>
       <c r="F10" t="n">
-        <v>19.85473664223811</v>
+        <v>21.92659929177112</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[15804.530505583803, 7352.48564264846, 12540.53413918472, 10567.617104196685, 16224.58087520054, 6304.662927773441, 14882.961856025282]</t>
+          <t>[15997.903107701557, 7112.336138538036, 12217.92407121556, 10522.924894735539, 16414.114916727103, 6626.84241203229, 15049.601797440831]</t>
         </is>
       </c>
     </row>
@@ -738,20 +738,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>517.8259842842961</v>
+        <v>795.1104098653934</v>
       </c>
       <c r="D11" t="n">
-        <v>474.6428571428572</v>
+        <v>702.2496884627445</v>
       </c>
       <c r="E11" t="n">
-        <v>25.45760695582581</v>
+        <v>35.3367668992926</v>
       </c>
       <c r="F11" t="n">
-        <v>23.27907761243296</v>
+        <v>34.67014287668622</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[2370.0, 2437.5, 2190.0, 2250.0, 2280.0, 2070.0, 1500.0]</t>
+          <t>[2362.0030236900257, 2160.014606499174, 1985.0045424901864, 1866.1844272141072, 1495.4618151869408, 2210.5049605251784, 1719.8961414340433]</t>
         </is>
       </c>
     </row>
@@ -763,24 +763,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1420.010415255802</v>
+        <v>2335.22176982952</v>
       </c>
       <c r="D12" t="n">
-        <v>1332.325383459975</v>
+        <v>2226.428571428572</v>
       </c>
       <c r="E12" t="n">
-        <v>98.25719320775146</v>
+        <v>169.2589685446828</v>
       </c>
       <c r="F12" t="n">
-        <v>52.04208266886434</v>
+        <v>74.44203483460929</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[6111.073835388541, 1295.4995790796847, 2767.8302517456227, 3875.676701254244, 3936.3284318154797, 2542.4774242520825, 3213.4469625390147]</t>
+          <t>[4350.0, 2010.0, 1860.0, 3480.0, 5100.0, 3900.0, 3255.0]</t>
         </is>
       </c>
     </row>
@@ -796,20 +796,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>992.753209421116</v>
+        <v>1059.858366272127</v>
       </c>
       <c r="D13" t="n">
-        <v>814.0009416852679</v>
+        <v>946.2747628348214</v>
       </c>
       <c r="E13" t="n">
-        <v>18.59088280657533</v>
+        <v>23.38905551596172</v>
       </c>
       <c r="F13" t="n">
-        <v>17.85731333743497</v>
+        <v>21.81070290497255</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[5609.9248046875, 5322.5224609375, 4912.474609375, 4564.01220703125, 4158.380859375, 3505.139892578125, 3143.419921875]</t>
+          <t>[5696.66162109375, 5773.73974609375, 4454.2109375, 4727.28125, 3828.8251953125, 3392.5810546875, 4312.06103515625]</t>
         </is>
       </c>
     </row>
@@ -825,20 +825,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5850.373394578911</v>
+        <v>5850.386323273816</v>
       </c>
       <c r="D14" t="n">
-        <v>4285.184474897358</v>
+        <v>4285.186933465739</v>
       </c>
       <c r="E14" t="n">
-        <v>45.92048225574732</v>
+        <v>45.92005583475944</v>
       </c>
       <c r="F14" t="n">
-        <v>39.34371447603629</v>
+        <v>39.34335287898115</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[20603.561678904407, 1925.3904316009994, 7964.017465293877, 13717.609449823954, 7801.808803245047, 6523.128939719058, 6065.607837815738]</t>
+          <t>[20603.591743652156, 1925.3283839808355, 7963.964832871674, 13717.653238743595, 7801.810249843373, 6523.149402145296, 6065.5688172900045]</t>
         </is>
       </c>
     </row>
@@ -854,20 +854,20 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1315.341770396994</v>
+        <v>1452.756872962798</v>
       </c>
       <c r="D15" t="n">
-        <v>925.5544607979911</v>
+        <v>1200.945870535714</v>
       </c>
       <c r="E15" t="n">
-        <v>46.55200848933864</v>
+        <v>55.69214550720426</v>
       </c>
       <c r="F15" t="n">
-        <v>32.38429815182426</v>
+        <v>40.59547326319695</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[4792.2587890625, 3439.514892578125, 1850.7491455078125, 4826.494140625, 7691.54638671875, 2095.781982421875, 2915.341552734375]</t>
+          <t>[4607.6328125, 3306.841552734375, 2118.6025390625, 4451.60986328125, 6878.49609375, 2469.4462890625, 2472.113037109375]</t>
         </is>
       </c>
     </row>
@@ -879,24 +879,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1176.384776702395</v>
+        <v>894.7834868969376</v>
       </c>
       <c r="D16" t="n">
-        <v>905.1428571428571</v>
+        <v>751.9453753755477</v>
       </c>
       <c r="E16" t="n">
-        <v>30.70207690503257</v>
+        <v>34.7774191068043</v>
       </c>
       <c r="F16" t="n">
-        <v>25.9873794942311</v>
+        <v>27.66158042950298</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[4056.0, 1752.0, 840.0, 4248.0, 5184.0, 4512.0, 2088.0]</t>
+          <t>[3116.6119789239765, 1823.1544322767845, 1153.3182293623472, 4419.92901766762, 5542.47640886455, 5220.673823326314, 2953.612236924209]</t>
         </is>
       </c>
     </row>
@@ -908,24 +908,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1380.719857824924</v>
+        <v>781.1833643117697</v>
       </c>
       <c r="D17" t="n">
-        <v>945.5927643784798</v>
+        <v>620.5340909973189</v>
       </c>
       <c r="E17" t="n">
-        <v>17.9948133361219</v>
+        <v>15.13417023248813</v>
       </c>
       <c r="F17" t="n">
-        <v>18.52461482887329</v>
+        <v>15.40645172527614</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[4904.0, 3067.5, 2515.555555555551, 6878.181818181829, 6878.181818181829, 2515.555555555551, 4925.714285714299]</t>
+          <t>[4913.294285830711, 2474.0819305780087, 3221.7729473025383, 4265.123250690064, 8085.676550491806, 3074.750035834744, 7854.038570450928]</t>
         </is>
       </c>
     </row>
@@ -937,24 +937,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1972.228616247352</v>
+        <v>2250.749867039444</v>
       </c>
       <c r="D18" t="n">
-        <v>1660.195197005412</v>
+        <v>2048.69548229546</v>
       </c>
       <c r="E18" t="n">
-        <v>46.22391759420674</v>
+        <v>74.51987998169078</v>
       </c>
       <c r="F18" t="n">
-        <v>40.04676676687783</v>
+        <v>51.89306467489615</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[2480.2082120199384, 4843.758553345192, 2759.21277096713, 3576.9204762775635, 4098.295445500262, 2423.9764077013433, 7596.943463472491]</t>
+          <t>[3182.399999999979, 3848.88888888893, 3182.399999999979, 4288.0, 3848.88888888893, 4288.0, 6793.846153846121]</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>551.4972393028328</v>
+        <v>572.4789678722336</v>
       </c>
       <c r="D19" t="n">
-        <v>416.4160886763325</v>
+        <v>427.99818124566</v>
       </c>
       <c r="E19" t="n">
-        <v>13.7798501515094</v>
+        <v>14.36465730651615</v>
       </c>
       <c r="F19" t="n">
-        <v>40.19114222645599</v>
+        <v>40.65595488496046</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[2788.8069748541443, 1572.5747494509978, 851.5273729796762, 2240.9588587465687, 3369.1257040912205, 2050.407362410465, 1738.3192761231667]</t>
+          <t>[2753.9737866731266, 1613.5831747091695, 865.2999776085996, 2235.1541998644743, 3311.3172806868215, 2030.8182732297068, 1721.216462949687]</t>
         </is>
       </c>
     </row>
@@ -1028,20 +1028,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1629.934277897529</v>
+        <v>3130.748123371124</v>
       </c>
       <c r="D21" t="n">
-        <v>1184.657823688758</v>
+        <v>2808.920806195413</v>
       </c>
       <c r="E21" t="n">
-        <v>8.366989826403785</v>
+        <v>25.80381798341445</v>
       </c>
       <c r="F21" t="n">
-        <v>8.476501542440051</v>
+        <v>23.30483197674868</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[12525.648731290692, 17000.08489702294, 10563.146820876957, 17305.734065262634, 13941.76699353795, 5711.458265453375, 8837.146565069444]</t>
+          <t>[13368.327049369067, 14947.528277402229, 12300.103011726245, 15806.68221972699, 14442.011815947297, 9306.165487202896, 11884.072408146205]</t>
         </is>
       </c>
     </row>
@@ -1053,24 +1053,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>672.2812390364845</v>
+        <v>992.6258598145204</v>
       </c>
       <c r="D22" t="n">
-        <v>565.9896460342762</v>
+        <v>881.1731212902799</v>
       </c>
       <c r="E22" t="n">
-        <v>14.81116852684553</v>
+        <v>21.95712944809437</v>
       </c>
       <c r="F22" t="n">
-        <v>13.40030052713239</v>
+        <v>20.48791252932092</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[4391.246726250073, 5273.843785545822, 4245.793829832383, 4867.215363028351, 4832.692876346163, 4388.555720531725, 4688.597606426885]</t>
+          <t>[4244.432493669708, 3350.219590453109, 5259.292949972595, 4665.223470749421, 5283.100755103338, 4704.508035064897, 5192.320676423952]</t>
         </is>
       </c>
     </row>
@@ -1082,24 +1082,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2162.601903531532</v>
+        <v>1803.508624161209</v>
       </c>
       <c r="D23" t="n">
-        <v>1812.7822265625</v>
+        <v>1594.203406228075</v>
       </c>
       <c r="E23" t="n">
-        <v>12.58330233134921</v>
+        <v>12.09785958021593</v>
       </c>
       <c r="F23" t="n">
-        <v>11.66198053453604</v>
+        <v>11.46790370908964</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[12819.28125, 20588.904296875, 9646.4111328125, 12362.548828125, 16750.431640625, 20021.28515625, 18268.28125]</t>
+          <t>[15112.28665143269, 15591.851245713491, 10336.470408918634, 14876.76286715149, 14314.598406468736, 20632.481562694884, 16143.638318033349]</t>
         </is>
       </c>
     </row>
@@ -1115,20 +1115,20 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>413.8149702890145</v>
+        <v>413.7729711229493</v>
       </c>
       <c r="D24" t="n">
-        <v>344.088356200472</v>
+        <v>344.0572537128952</v>
       </c>
       <c r="E24" t="n">
-        <v>15.52189482129971</v>
+        <v>15.52030582211568</v>
       </c>
       <c r="F24" t="n">
-        <v>13.97206096788417</v>
+        <v>13.9710489461656</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[3859.827920612819, 3025.827876031685, 2360.0761006224247, 3726.888992033889, 2723.43812107102, 1955.8355829493055, 3270.705044253959]</t>
+          <t>[3859.702641833315, 3025.593791744376, 2359.9543787941575, 3726.878971607327, 2723.509237128749, 1955.8328830281966, 3270.5586388714432]</t>
         </is>
       </c>
     </row>
@@ -1140,24 +1140,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4599.082630737352</v>
+        <v>4859.452030726929</v>
       </c>
       <c r="D25" t="n">
-        <v>3026.819308806079</v>
+        <v>3256.778738839286</v>
       </c>
       <c r="E25" t="n">
-        <v>83.25034381905633</v>
+        <v>87.59254543614323</v>
       </c>
       <c r="F25" t="n">
-        <v>37.67277169458151</v>
+        <v>39.15755353610545</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[13388.886260297646, 13470.226857199561, 13024.50509413984, 12331.026671320726, 13114.239408112408, 9423.363255643299, 10353.713849923486]</t>
+          <t>[12768.94921875, 13684.830078125, 13624.8984375, 11851.2275390625, 13746.0263671875, 9526.2001953125, 9994.6669921875]</t>
         </is>
       </c>
     </row>
@@ -1169,24 +1169,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>945.0118080653002</v>
+        <v>1147.680891437785</v>
       </c>
       <c r="D26" t="n">
-        <v>754.177579585467</v>
+        <v>1014.285714285714</v>
       </c>
       <c r="E26" t="n">
-        <v>149.9827992208392</v>
+        <v>153.9473684210526</v>
       </c>
       <c r="F26" t="n">
-        <v>82.58326196124925</v>
+        <v>143.0673083611555</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[1062.6604281415382, 1607.4900071793688, 128.58895434818726, 0.0, 0.0, 1962.2028722107368, 1300.1155516637145]</t>
+          <t>[1180.0, 1600.0, 200.0, 380.0, 540.0, 1420.0, 980.0]</t>
         </is>
       </c>
     </row>
